--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/74.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/74.xlsx
@@ -426,13 +426,13 @@
         <v>-8.766863988377875</v>
       </c>
       <c r="E2">
-        <v>-7.608703348129268</v>
+        <v>-6.262618977823261</v>
       </c>
       <c r="F2">
-        <v>-6.181091324271788</v>
+        <v>-5.762689576056981</v>
       </c>
       <c r="G2">
-        <v>-7.230358409167099</v>
+        <v>-7.809866095270981</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-8.869381709586495</v>
       </c>
       <c r="E3">
-        <v>-8.21257535705211</v>
+        <v>-7.0290813175175</v>
       </c>
       <c r="F3">
-        <v>-6.143159552530197</v>
+        <v>-5.932245614633803</v>
       </c>
       <c r="G3">
-        <v>-7.019986482328572</v>
+        <v>-7.560300619793022</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-9.081653772571389</v>
       </c>
       <c r="E4">
-        <v>-8.279805082169984</v>
+        <v>-7.471019624400058</v>
       </c>
       <c r="F4">
-        <v>-6.437098270106976</v>
+        <v>-6.042107841430088</v>
       </c>
       <c r="G4">
-        <v>-7.282443222136452</v>
+        <v>-7.954904405891991</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-9.384566113065619</v>
       </c>
       <c r="E5">
-        <v>-9.373988557325319</v>
+        <v>-7.953406261119127</v>
       </c>
       <c r="F5">
-        <v>-6.322748362906025</v>
+        <v>-5.987846463077109</v>
       </c>
       <c r="G5">
-        <v>-7.245874936109662</v>
+        <v>-8.156629187781942</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-9.754838867839796</v>
       </c>
       <c r="E6">
-        <v>-10.86993824644117</v>
+        <v>-9.01946791268683</v>
       </c>
       <c r="F6">
-        <v>-6.189858764863018</v>
+        <v>-5.629257811548842</v>
       </c>
       <c r="G6">
-        <v>-7.252145109361043</v>
+        <v>-7.846825025671404</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-10.154227170867</v>
       </c>
       <c r="E7">
-        <v>-10.93527506942383</v>
+        <v>-10.54962569445662</v>
       </c>
       <c r="F7">
-        <v>-6.491817735633703</v>
+        <v>-5.803789853114282</v>
       </c>
       <c r="G7">
-        <v>-6.926145758472391</v>
+        <v>-8.102955312953737</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-10.54610895969029</v>
       </c>
       <c r="E8">
-        <v>-12.11634184689033</v>
+        <v>-11.53075581601046</v>
       </c>
       <c r="F8">
-        <v>-6.229158171186633</v>
+        <v>-5.585223457150826</v>
       </c>
       <c r="G8">
-        <v>-7.097549253768157</v>
+        <v>-7.992995542866845</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-10.88400693464881</v>
       </c>
       <c r="E9">
-        <v>-12.91413216976964</v>
+        <v>-11.09167497622675</v>
       </c>
       <c r="F9">
-        <v>-5.901561229299304</v>
+        <v>-5.456347713358085</v>
       </c>
       <c r="G9">
-        <v>-6.984560334512831</v>
+        <v>-7.552507595593578</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-11.13524074592572</v>
       </c>
       <c r="E10">
-        <v>-13.37115029509774</v>
+        <v>-12.21667471700428</v>
       </c>
       <c r="F10">
-        <v>-6.059336226673512</v>
+        <v>-5.624368787137519</v>
       </c>
       <c r="G10">
-        <v>-7.360088757214519</v>
+        <v>-6.961995656117159</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-11.2688015730136</v>
       </c>
       <c r="E11">
-        <v>-13.96341129666491</v>
+        <v>-13.95169613440707</v>
       </c>
       <c r="F11">
-        <v>-5.82103149223615</v>
+        <v>-5.210569448212666</v>
       </c>
       <c r="G11">
-        <v>-6.436823953949334</v>
+        <v>-7.070704039990207</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-11.27300458860527</v>
       </c>
       <c r="E12">
-        <v>-15.69112828549333</v>
+        <v>-14.94780644797829</v>
       </c>
       <c r="F12">
-        <v>-5.528783472528485</v>
+        <v>-5.385746787984885</v>
       </c>
       <c r="G12">
-        <v>-5.946115030845323</v>
+        <v>-6.854733980644772</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-11.14246716522695</v>
       </c>
       <c r="E13">
-        <v>-15.57525369258506</v>
+        <v>-15.91865240506071</v>
       </c>
       <c r="F13">
-        <v>-5.443735819650462</v>
+        <v>-4.991086049534311</v>
       </c>
       <c r="G13">
-        <v>-5.435109153040041</v>
+        <v>-5.924073418644856</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-10.88706136794261</v>
       </c>
       <c r="E14">
-        <v>-16.63973943519809</v>
+        <v>-16.11631576702151</v>
       </c>
       <c r="F14">
-        <v>-5.286558075173673</v>
+        <v>-4.884345939479179</v>
       </c>
       <c r="G14">
-        <v>-5.361621663159299</v>
+        <v>-5.549326284690436</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-10.5266894914176</v>
       </c>
       <c r="E15">
-        <v>-18.12487965685763</v>
+        <v>-17.8028643986462</v>
       </c>
       <c r="F15">
-        <v>-5.534391519845437</v>
+        <v>-4.790991418285882</v>
       </c>
       <c r="G15">
-        <v>-4.929731202651519</v>
+        <v>-5.226061444417223</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-10.08394738836456</v>
       </c>
       <c r="E16">
-        <v>-18.59128983727764</v>
+        <v>-18.82551609837638</v>
       </c>
       <c r="F16">
-        <v>-4.966153847444851</v>
+        <v>-4.573649349343765</v>
       </c>
       <c r="G16">
-        <v>-3.983832199534338</v>
+        <v>-3.977658032103597</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-9.591625930025206</v>
       </c>
       <c r="E17">
-        <v>-20.38446591788693</v>
+        <v>-19.20346253905654</v>
       </c>
       <c r="F17">
-        <v>-4.992435460033472</v>
+        <v>-4.224396398445048</v>
       </c>
       <c r="G17">
-        <v>-3.152676704808296</v>
+        <v>-3.86603636815599</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-9.076905087610294</v>
       </c>
       <c r="E18">
-        <v>-20.48189603616196</v>
+        <v>-20.40433233335858</v>
       </c>
       <c r="F18">
-        <v>-4.203486748463583</v>
+        <v>-4.212350279673538</v>
       </c>
       <c r="G18">
-        <v>-4.028709954864699</v>
+        <v>-3.410184179034966</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-8.574805728916933</v>
       </c>
       <c r="E19">
-        <v>-21.62665803750897</v>
+        <v>-21.77445837217131</v>
       </c>
       <c r="F19">
-        <v>-4.437676153643837</v>
+        <v>-3.76395334780336</v>
       </c>
       <c r="G19">
-        <v>-2.876984403934409</v>
+        <v>-2.976327254476859</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-8.111517565789972</v>
       </c>
       <c r="E20">
-        <v>-22.04623021126764</v>
+        <v>-22.34627784206786</v>
       </c>
       <c r="F20">
-        <v>-4.231469827697554</v>
+        <v>-3.659521069332426</v>
       </c>
       <c r="G20">
-        <v>-3.029895191847806</v>
+        <v>-3.012216878668098</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-7.71298792496134</v>
       </c>
       <c r="E21">
-        <v>-23.02591574961304</v>
+        <v>-23.80182901456129</v>
       </c>
       <c r="F21">
-        <v>-3.6652831929863</v>
+        <v>-3.376118356751854</v>
       </c>
       <c r="G21">
-        <v>-3.156295131082719</v>
+        <v>-2.338908195254506</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-7.397236708442104</v>
       </c>
       <c r="E22">
-        <v>-24.75581546291315</v>
+        <v>-23.72829565362473</v>
       </c>
       <c r="F22">
-        <v>-3.854860043321383</v>
+        <v>-3.208977009154192</v>
       </c>
       <c r="G22">
-        <v>-3.045918232257879</v>
+        <v>-1.865659089324611</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-7.169402666121234</v>
       </c>
       <c r="E23">
-        <v>-24.6379438129675</v>
+        <v>-24.62221189426485</v>
       </c>
       <c r="F23">
-        <v>-3.845680075763559</v>
+        <v>-3.245633923462876</v>
       </c>
       <c r="G23">
-        <v>-2.491411786066573</v>
+        <v>-2.673236878719964</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-7.033205588438304</v>
       </c>
       <c r="E24">
-        <v>-25.43183059125219</v>
+        <v>-25.67436207368099</v>
       </c>
       <c r="F24">
-        <v>-3.490046210761078</v>
+        <v>-2.955904140659721</v>
       </c>
       <c r="G24">
-        <v>-2.616318669263274</v>
+        <v>-2.455959153886517</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-6.975335170876559</v>
       </c>
       <c r="E25">
-        <v>-24.90564002545693</v>
+        <v>-26.23296745642316</v>
       </c>
       <c r="F25">
-        <v>-3.595553710120846</v>
+        <v>-3.043121287765675</v>
       </c>
       <c r="G25">
-        <v>-3.407376836417664</v>
+        <v>-2.864728764348027</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-6.982971443785382</v>
       </c>
       <c r="E26">
-        <v>-26.49003081194258</v>
+        <v>-26.226967228363</v>
       </c>
       <c r="F26">
-        <v>-3.103776005733461</v>
+        <v>-2.526835505399064</v>
       </c>
       <c r="G26">
-        <v>-3.318872711970788</v>
+        <v>-2.865559711278384</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-7.030618787794865</v>
       </c>
       <c r="E27">
-        <v>-26.64948743870067</v>
+        <v>-25.39615980149377</v>
       </c>
       <c r="F27">
-        <v>-3.367241571663455</v>
+        <v>-2.917472863374241</v>
       </c>
       <c r="G27">
-        <v>-4.418433996838781</v>
+        <v>-3.015596945663694</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-7.092623557408174</v>
       </c>
       <c r="E28">
-        <v>-25.19466987899649</v>
+        <v>-25.74514212242088</v>
       </c>
       <c r="F28">
-        <v>-3.447191451544649</v>
+        <v>-2.913698821487086</v>
       </c>
       <c r="G28">
-        <v>-3.875050983659426</v>
+        <v>-2.827084551020975</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-7.142574216605706</v>
       </c>
       <c r="E29">
-        <v>-25.87552141757572</v>
+        <v>-26.23069869094532</v>
       </c>
       <c r="F29">
-        <v>-3.434942382759453</v>
+        <v>-2.898113088803413</v>
       </c>
       <c r="G29">
-        <v>-3.696582784182855</v>
+        <v>-3.527774756589878</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-7.153881452908242</v>
       </c>
       <c r="E30">
-        <v>-25.17931382363648</v>
+        <v>-25.46895502116707</v>
       </c>
       <c r="F30">
-        <v>-3.542857117791755</v>
+        <v>-2.804124038179573</v>
       </c>
       <c r="G30">
-        <v>-2.987871126772298</v>
+        <v>-2.985937768177363</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-7.112754659217342</v>
       </c>
       <c r="E31">
-        <v>-25.2330532246855</v>
+        <v>-25.38984710872708</v>
       </c>
       <c r="F31">
-        <v>-3.794558209867191</v>
+        <v>-3.06762605227529</v>
       </c>
       <c r="G31">
-        <v>-4.10174390000656</v>
+        <v>-3.161039142840495</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-7.007805293822387</v>
       </c>
       <c r="E32">
-        <v>-24.92854957546173</v>
+        <v>-25.66597533981879</v>
       </c>
       <c r="F32">
-        <v>-3.613570701131735</v>
+        <v>-3.050775402567543</v>
       </c>
       <c r="G32">
-        <v>-3.641296673677027</v>
+        <v>-2.804155712615982</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-6.841992209115313</v>
       </c>
       <c r="E33">
-        <v>-23.46145079424875</v>
+        <v>-25.43869575784782</v>
       </c>
       <c r="F33">
-        <v>-3.330912690846279</v>
+        <v>-2.917040455589979</v>
       </c>
       <c r="G33">
-        <v>-3.844209941415575</v>
+        <v>-3.079987056402518</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-6.62314004713334</v>
       </c>
       <c r="E34">
-        <v>-24.12444655981574</v>
+        <v>-24.40008571571462</v>
       </c>
       <c r="F34">
-        <v>-3.383982876874033</v>
+        <v>-3.141065792737883</v>
       </c>
       <c r="G34">
-        <v>-3.533065008361634</v>
+        <v>-2.505216760965333</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-6.365468329508087</v>
       </c>
       <c r="E35">
-        <v>-23.9245234893251</v>
+        <v>-24.27342882619408</v>
       </c>
       <c r="F35">
-        <v>-3.632836870186046</v>
+        <v>-3.189172401288062</v>
       </c>
       <c r="G35">
-        <v>-3.400471038422744</v>
+        <v>-3.256435823100134</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-6.090581677825955</v>
       </c>
       <c r="E36">
-        <v>-22.34301281230833</v>
+        <v>-23.28952275007354</v>
       </c>
       <c r="F36">
-        <v>-3.609529096573477</v>
+        <v>-3.027412956706388</v>
       </c>
       <c r="G36">
-        <v>-3.674491513799299</v>
+        <v>-2.067774515588196</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-5.818701641471256</v>
       </c>
       <c r="E37">
-        <v>-22.68621227192764</v>
+        <v>-22.90217519735344</v>
       </c>
       <c r="F37">
-        <v>-3.349247774939843</v>
+        <v>-2.941004296185566</v>
       </c>
       <c r="G37">
-        <v>-3.614319038077506</v>
+        <v>-2.861007711161887</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-5.575525012114913</v>
       </c>
       <c r="E38">
-        <v>-21.96446408458515</v>
+        <v>-22.6139831115053</v>
       </c>
       <c r="F38">
-        <v>-3.404737622151174</v>
+        <v>-3.044439220303529</v>
       </c>
       <c r="G38">
-        <v>-2.939798694996541</v>
+        <v>-2.546366842018474</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-5.379487917565354</v>
       </c>
       <c r="E39">
-        <v>-22.0136206699384</v>
+        <v>-22.63955993270062</v>
       </c>
       <c r="F39">
-        <v>-3.220302448285267</v>
+        <v>-3.244455985016095</v>
       </c>
       <c r="G39">
-        <v>-2.842604388509078</v>
+        <v>-2.107964538434948</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-5.246849389084984</v>
       </c>
       <c r="E40">
-        <v>-21.95621320494317</v>
+        <v>-21.929545021512</v>
       </c>
       <c r="F40">
-        <v>-3.547139777264229</v>
+        <v>-3.245648005708723</v>
       </c>
       <c r="G40">
-        <v>-2.610147812378073</v>
+        <v>-2.29850629749324</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-5.187435706222853</v>
       </c>
       <c r="E41">
-        <v>-20.65040055398737</v>
+        <v>-20.84515210716125</v>
       </c>
       <c r="F41">
-        <v>-3.383573663377049</v>
+        <v>-3.15209301960395</v>
       </c>
       <c r="G41">
-        <v>-2.134637603844856</v>
+        <v>-1.727082963596259</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-5.200146829664815</v>
       </c>
       <c r="E42">
-        <v>-20.1603336253513</v>
+        <v>-19.64582199402182</v>
       </c>
       <c r="F42">
-        <v>-3.184857435486879</v>
+        <v>-3.232660861567633</v>
       </c>
       <c r="G42">
-        <v>-2.274905418343776</v>
+        <v>-1.745625329161717</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-5.281242771000616</v>
       </c>
       <c r="E43">
-        <v>-19.49860130403245</v>
+        <v>-20.52410594238746</v>
       </c>
       <c r="F43">
-        <v>-3.467921345799706</v>
+        <v>-3.108955787103166</v>
       </c>
       <c r="G43">
-        <v>-2.774837521320197</v>
+        <v>-1.974903781575021</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-5.417964005696996</v>
       </c>
       <c r="E44">
-        <v>-18.82457870425679</v>
+        <v>-18.71749840787141</v>
       </c>
       <c r="F44">
-        <v>-3.61224945512427</v>
+        <v>-3.225032426155252</v>
       </c>
       <c r="G44">
-        <v>-1.93589231294025</v>
+        <v>-1.559910345499682</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-5.601202466095149</v>
       </c>
       <c r="E45">
-        <v>-18.27314189586876</v>
+        <v>-18.44374762563373</v>
       </c>
       <c r="F45">
-        <v>-3.686336150528449</v>
+        <v>-3.331425450268612</v>
       </c>
       <c r="G45">
-        <v>-1.837112255139476</v>
+        <v>-1.651953443128038</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-5.817416174841249</v>
       </c>
       <c r="E46">
-        <v>-18.73409979358353</v>
+        <v>-17.48451720438098</v>
       </c>
       <c r="F46">
-        <v>-3.577660145852974</v>
+        <v>-3.038006947420791</v>
       </c>
       <c r="G46">
-        <v>-2.164127943508684</v>
+        <v>-1.189731764389456</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-6.052698554078865</v>
       </c>
       <c r="E47">
-        <v>-17.15660134453756</v>
+        <v>-17.23198685134324</v>
       </c>
       <c r="F47">
-        <v>-3.692787475861452</v>
+        <v>-3.23354472958642</v>
       </c>
       <c r="G47">
-        <v>-2.214670042256737</v>
+        <v>-1.032749005462756</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-6.297114219848004</v>
       </c>
       <c r="E48">
-        <v>-17.39948151946495</v>
+        <v>-16.95242150847972</v>
       </c>
       <c r="F48">
-        <v>-3.806493327406726</v>
+        <v>-3.299946660594828</v>
       </c>
       <c r="G48">
-        <v>-2.389758174737711</v>
+        <v>-1.195187543438175</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-6.536479249210194</v>
       </c>
       <c r="E49">
-        <v>-15.41757675611199</v>
+        <v>-15.91843050983434</v>
       </c>
       <c r="F49">
-        <v>-3.786276192574001</v>
+        <v>-3.090238825636911</v>
       </c>
       <c r="G49">
-        <v>-2.79830597864809</v>
+        <v>-1.711722032294041</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-6.765401496551616</v>
       </c>
       <c r="E50">
-        <v>-15.30106364836863</v>
+        <v>-15.48182221685881</v>
       </c>
       <c r="F50">
-        <v>-3.742361123081988</v>
+        <v>-3.63237049933827</v>
       </c>
       <c r="G50">
-        <v>-2.136991401723278</v>
+        <v>-1.508580336913282</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-6.976302890692661</v>
       </c>
       <c r="E51">
-        <v>-15.06266213423483</v>
+        <v>-14.38892029984764</v>
       </c>
       <c r="F51">
-        <v>-3.633852448621878</v>
+        <v>-3.363481612022147</v>
       </c>
       <c r="G51">
-        <v>-2.810111384041131</v>
+        <v>-1.469654942462531</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-7.168286761978529</v>
       </c>
       <c r="E52">
-        <v>-15.00769551672973</v>
+        <v>-14.11989271599996</v>
       </c>
       <c r="F52">
-        <v>-3.92254263033452</v>
+        <v>-3.441379625846607</v>
       </c>
       <c r="G52">
-        <v>-3.341645954735434</v>
+        <v>-1.569530790836804</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-7.342746387581117</v>
       </c>
       <c r="E53">
-        <v>-14.79976610419353</v>
+        <v>-13.85051191117968</v>
       </c>
       <c r="F53">
-        <v>-4.262723301437776</v>
+        <v>-3.531792614392562</v>
       </c>
       <c r="G53">
-        <v>-2.042524984760175</v>
+        <v>-1.378581834677181</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-7.500625833734113</v>
       </c>
       <c r="E54">
-        <v>-13.89168026838341</v>
+        <v>-12.89823269752871</v>
       </c>
       <c r="F54">
-        <v>-3.967218969469706</v>
+        <v>-3.66227704768154</v>
       </c>
       <c r="G54">
-        <v>-2.399050876066446</v>
+        <v>-1.712731748683518</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-7.651124782988333</v>
       </c>
       <c r="E55">
-        <v>-13.40706562245257</v>
+        <v>-12.44484640835476</v>
       </c>
       <c r="F55">
-        <v>-3.751794571065069</v>
+        <v>-3.792076421128403</v>
       </c>
       <c r="G55">
-        <v>-2.475987954399108</v>
+        <v>-1.697089421010462</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-7.796889338751607</v>
       </c>
       <c r="E56">
-        <v>-13.09800179990308</v>
+        <v>-11.32838736955569</v>
       </c>
       <c r="F56">
-        <v>-3.971813923453035</v>
+        <v>-3.772538547565974</v>
       </c>
       <c r="G56">
-        <v>-2.893484162902137</v>
+        <v>-1.855293771241153</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-7.948974766842488</v>
       </c>
       <c r="E57">
-        <v>-12.10342211054645</v>
+        <v>-12.20068467528319</v>
       </c>
       <c r="F57">
-        <v>-4.096072347342572</v>
+        <v>-4.011515916334409</v>
       </c>
       <c r="G57">
-        <v>-2.562591825706443</v>
+        <v>-1.526785026833734</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-8.111928784282993</v>
       </c>
       <c r="E58">
-        <v>-12.34346293227103</v>
+        <v>-10.28850935470034</v>
       </c>
       <c r="F58">
-        <v>-3.91301474846752</v>
+        <v>-3.915904093968485</v>
       </c>
       <c r="G58">
-        <v>-3.055820073965839</v>
+        <v>-1.444554386183777</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-8.291675245267459</v>
       </c>
       <c r="E59">
-        <v>-11.38568615117475</v>
+        <v>-10.45472699315188</v>
       </c>
       <c r="F59">
-        <v>-4.279401650725742</v>
+        <v>-3.896952704527238</v>
       </c>
       <c r="G59">
-        <v>-2.782849041525233</v>
+        <v>-1.503521823329276</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-8.491882550409128</v>
       </c>
       <c r="E60">
-        <v>-10.69839512255661</v>
+        <v>-9.838184313955576</v>
       </c>
       <c r="F60">
-        <v>-4.310372651181609</v>
+        <v>-3.853486610167542</v>
       </c>
       <c r="G60">
-        <v>-2.731717665671189</v>
+        <v>-1.583736341745816</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-8.71156309714617</v>
       </c>
       <c r="E61">
-        <v>-10.45353600448786</v>
+        <v>-9.625327921699039</v>
       </c>
       <c r="F61">
-        <v>-4.362377556729363</v>
+        <v>-3.877484413826644</v>
       </c>
       <c r="G61">
-        <v>-3.512261540192854</v>
+        <v>-2.165637552274592</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-8.95586924033617</v>
       </c>
       <c r="E62">
-        <v>-10.63733770751119</v>
+        <v>-8.943969194030949</v>
       </c>
       <c r="F62">
-        <v>-4.234461062389062</v>
+        <v>-3.778434038371698</v>
       </c>
       <c r="G62">
-        <v>-3.248526929806815</v>
+        <v>-1.927788097460114</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-9.219416874137734</v>
       </c>
       <c r="E63">
-        <v>-10.46198160851217</v>
+        <v>-8.332706715527589</v>
       </c>
       <c r="F63">
-        <v>-4.319505401797474</v>
+        <v>-3.854472367376873</v>
       </c>
       <c r="G63">
-        <v>-3.407542363694628</v>
+        <v>-2.65540296989991</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-9.504750508845447</v>
       </c>
       <c r="E64">
-        <v>-10.09198716818947</v>
+        <v>-9.013762035437164</v>
       </c>
       <c r="F64">
-        <v>-4.163764874764541</v>
+        <v>-4.058317017857775</v>
       </c>
       <c r="G64">
-        <v>-2.596134273110338</v>
+        <v>-2.461547354756807</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-9.806102824389471</v>
       </c>
       <c r="E65">
-        <v>-9.854586446811359</v>
+        <v>-8.897516107660266</v>
       </c>
       <c r="F65">
-        <v>-4.161694784624945</v>
+        <v>-4.059518150591835</v>
       </c>
       <c r="G65">
-        <v>-3.955364818442145</v>
+        <v>-2.567839040386187</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-10.11917353852542</v>
       </c>
       <c r="E66">
-        <v>-9.14429982718227</v>
+        <v>-8.378797523977658</v>
       </c>
       <c r="F66">
-        <v>-4.185363726425136</v>
+        <v>-3.507407963156353</v>
       </c>
       <c r="G66">
-        <v>-3.719336163674266</v>
+        <v>-2.763293649024758</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-10.43778054202047</v>
       </c>
       <c r="E67">
-        <v>-9.20941928341257</v>
+        <v>-7.243685700740999</v>
       </c>
       <c r="F67">
-        <v>-4.35297641507499</v>
+        <v>-3.981159564491418</v>
       </c>
       <c r="G67">
-        <v>-3.582501384899571</v>
+        <v>-2.6895181416821</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-10.7507935197732</v>
       </c>
       <c r="E68">
-        <v>-10.22997429967719</v>
+        <v>-7.960411810408994</v>
       </c>
       <c r="F68">
-        <v>-4.118420043135297</v>
+        <v>-3.9095173812929</v>
       </c>
       <c r="G68">
-        <v>-4.038982577673057</v>
+        <v>-2.653022687657174</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-11.05491034551466</v>
       </c>
       <c r="E69">
-        <v>-8.596195975663889</v>
+        <v>-7.349488967456208</v>
       </c>
       <c r="F69">
-        <v>-4.535972714762235</v>
+        <v>-3.844757274476841</v>
       </c>
       <c r="G69">
-        <v>-3.936640372872027</v>
+        <v>-2.530141858330506</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-11.33728769801172</v>
       </c>
       <c r="E70">
-        <v>-9.138593949932606</v>
+        <v>-7.780414025552112</v>
       </c>
       <c r="F70">
-        <v>-4.527868796460647</v>
+        <v>-3.718460238409014</v>
       </c>
       <c r="G70">
-        <v>-4.197494808638901</v>
+        <v>-2.916197815847076</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-11.59449881167159</v>
       </c>
       <c r="E71">
-        <v>-9.017339529903225</v>
+        <v>-7.448042147285139</v>
       </c>
       <c r="F71">
-        <v>-4.271185074457373</v>
+        <v>-4.050775561022689</v>
       </c>
       <c r="G71">
-        <v>-3.896248406747379</v>
+        <v>-3.151739820420682</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-11.81719341095167</v>
       </c>
       <c r="E72">
-        <v>-8.380436831568435</v>
+        <v>-6.93848013804604</v>
       </c>
       <c r="F72">
-        <v>-4.515340567860708</v>
+        <v>-3.922413405019683</v>
       </c>
       <c r="G72">
-        <v>-3.881635658737036</v>
+        <v>-2.971291914711628</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-12.00187708485997</v>
       </c>
       <c r="E73">
-        <v>-9.560919435887943</v>
+        <v>-7.740522698018544</v>
       </c>
       <c r="F73">
-        <v>-4.458449951371243</v>
+        <v>-4.055638906044525</v>
       </c>
       <c r="G73">
-        <v>-3.823297225244</v>
+        <v>-2.712913767008129</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-12.14803830522678</v>
       </c>
       <c r="E74">
-        <v>-9.597980467166717</v>
+        <v>-7.442775532014218</v>
       </c>
       <c r="F74">
-        <v>-4.458738223227417</v>
+        <v>-4.106534627639929</v>
       </c>
       <c r="G74">
-        <v>-3.833510258232651</v>
+        <v>-2.734041668639758</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-12.25374805707107</v>
       </c>
       <c r="E75">
-        <v>-9.244917991158697</v>
+        <v>-7.812403165942295</v>
       </c>
       <c r="F75">
-        <v>-4.394898432595868</v>
+        <v>-4.122719269955826</v>
       </c>
       <c r="G75">
-        <v>-3.332260558131601</v>
+        <v>-2.026415870166081</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-12.32481755534885</v>
       </c>
       <c r="E76">
-        <v>-10.12293023108388</v>
+        <v>-8.355711363486554</v>
       </c>
       <c r="F76">
-        <v>-4.683154549789442</v>
+        <v>-4.414842206185669</v>
       </c>
       <c r="G76">
-        <v>-3.170454334354182</v>
+        <v>-1.822684897679332</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-12.35795791110107</v>
       </c>
       <c r="E77">
-        <v>-9.404759538207438</v>
+        <v>-9.121585001559795</v>
       </c>
       <c r="F77">
-        <v>-4.537895355504133</v>
+        <v>-4.586923108606224</v>
       </c>
       <c r="G77">
-        <v>-2.004387500147771</v>
+        <v>-2.001014054243253</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-12.3602972618639</v>
       </c>
       <c r="E78">
-        <v>-9.925067616266739</v>
+        <v>-9.790893459893475</v>
       </c>
       <c r="F78">
-        <v>-4.890390536417407</v>
+        <v>-4.359271178968864</v>
       </c>
       <c r="G78">
-        <v>-2.593909586507948</v>
+        <v>-2.110162740673024</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-12.33235275123458</v>
       </c>
       <c r="E79">
-        <v>-12.67659106569729</v>
+        <v>-9.292498667557291</v>
       </c>
       <c r="F79">
-        <v>-4.838755082731302</v>
+        <v>-4.230716013361006</v>
       </c>
       <c r="G79">
-        <v>-2.348740515506142</v>
+        <v>-0.8438923140839522</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-12.27984130149698</v>
       </c>
       <c r="E80">
-        <v>-11.7440831695638</v>
+        <v>-9.793302608065556</v>
       </c>
       <c r="F80">
-        <v>-4.980854883742334</v>
+        <v>-4.788571757102305</v>
       </c>
       <c r="G80">
-        <v>-2.751981514917068</v>
+        <v>-1.587834797123434</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-12.20616896519601</v>
       </c>
       <c r="E81">
-        <v>-11.28087009179321</v>
+        <v>-10.54761505199721</v>
       </c>
       <c r="F81">
-        <v>-5.106065930145091</v>
+        <v>-4.743334613235424</v>
       </c>
       <c r="G81">
-        <v>-2.282579262903807</v>
+        <v>-0.8532479157779326</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-12.11168146939273</v>
       </c>
       <c r="E82">
-        <v>-13.29275335307695</v>
+        <v>-11.39143278469048</v>
       </c>
       <c r="F82">
-        <v>-5.332718020327272</v>
+        <v>-4.692316293264406</v>
       </c>
       <c r="G82">
-        <v>-3.078007350170034</v>
+        <v>-0.77572156033928</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-12.00283334180331</v>
       </c>
       <c r="E83">
-        <v>-13.33928342350576</v>
+        <v>-12.59256523048496</v>
       </c>
       <c r="F83">
-        <v>-5.119396846758344</v>
+        <v>-4.911301843133677</v>
       </c>
       <c r="G83">
-        <v>-2.459322668154417</v>
+        <v>-0.6692809001606327</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-11.87723881614759</v>
       </c>
       <c r="E84">
-        <v>-13.84860089514845</v>
+        <v>-14.0119338956571</v>
       </c>
       <c r="F84">
-        <v>-5.228630342695904</v>
+        <v>-5.049138865489904</v>
       </c>
       <c r="G84">
-        <v>-1.857587979299868</v>
+        <v>-0.5842495379844522</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-11.74164406099305</v>
       </c>
       <c r="E85">
-        <v>-15.42440569491555</v>
+        <v>-14.42747572754895</v>
       </c>
       <c r="F85">
-        <v>-5.560987912047121</v>
+        <v>-5.170917157375459</v>
       </c>
       <c r="G85">
-        <v>-1.516631583664789</v>
+        <v>-0.6876742911768234</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-11.59620012322167</v>
       </c>
       <c r="E86">
-        <v>-16.34729511225675</v>
+        <v>-15.81398578532143</v>
       </c>
       <c r="F86">
-        <v>-5.340324089819777</v>
+        <v>-5.375805550783888</v>
       </c>
       <c r="G86">
-        <v>-1.934740243092583</v>
+        <v>-0.1718879856128332</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-11.45016011127147</v>
       </c>
       <c r="E87">
-        <v>-17.74330138002331</v>
+        <v>-16.66787484420775</v>
       </c>
       <c r="F87">
-        <v>-5.451671579369282</v>
+        <v>-5.275228494205583</v>
       </c>
       <c r="G87">
-        <v>-1.490431926266997</v>
+        <v>-0.5863550449474287</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-11.31205201885425</v>
       </c>
       <c r="E88">
-        <v>-19.12629281349183</v>
+        <v>-18.38216943607743</v>
       </c>
       <c r="F88">
-        <v>-5.766942414302954</v>
+        <v>-5.457345067711056</v>
       </c>
       <c r="G88">
-        <v>-1.59748503737041</v>
+        <v>0.3263127020465484</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-11.1862571485546</v>
       </c>
       <c r="E89">
-        <v>-21.44388429808538</v>
+        <v>-19.85856970290217</v>
       </c>
       <c r="F89">
-        <v>-5.865009517650776</v>
+        <v>-5.655337302491179</v>
       </c>
       <c r="G89">
-        <v>-1.743251668010059</v>
+        <v>-0.2234232480226678</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-11.0797852816393</v>
       </c>
       <c r="E90">
-        <v>-22.48183318301347</v>
+        <v>-20.90331582731577</v>
       </c>
       <c r="F90">
-        <v>-5.774569192980529</v>
+        <v>-5.606529066750829</v>
       </c>
       <c r="G90">
-        <v>-1.76836546647097</v>
+        <v>0.4419732315520659</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-10.98822786491355</v>
       </c>
       <c r="E91">
-        <v>-24.77917786031873</v>
+        <v>-22.92301976321075</v>
       </c>
       <c r="F91">
-        <v>-5.574285693964261</v>
+        <v>-5.44755542174477</v>
       </c>
       <c r="G91">
-        <v>-1.513771272318859</v>
+        <v>-0.1703783768469256</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-10.91474391171528</v>
       </c>
       <c r="E92">
-        <v>-26.71519559655196</v>
+        <v>-25.50592548296569</v>
       </c>
       <c r="F92">
-        <v>-5.720999501408888</v>
+        <v>-5.462880218696561</v>
       </c>
       <c r="G92">
-        <v>-1.80706905437059</v>
+        <v>-0.322368833100405</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-10.85117443928602</v>
       </c>
       <c r="E93">
-        <v>-28.34819955150996</v>
+        <v>-27.8908553760533</v>
       </c>
       <c r="F93">
-        <v>-5.579850666176268</v>
+        <v>-5.484492324235601</v>
       </c>
       <c r="G93">
-        <v>-2.154537293081415</v>
+        <v>-0.5448308722483503</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-10.79217490531042</v>
       </c>
       <c r="E94">
-        <v>-31.07418920024825</v>
+        <v>-29.87256541502394</v>
       </c>
       <c r="F94">
-        <v>-5.736183475902203</v>
+        <v>-5.554825686937695</v>
       </c>
       <c r="G94">
-        <v>-2.222125390811176</v>
+        <v>-0.545486360265126</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-10.73098923277534</v>
       </c>
       <c r="E95">
-        <v>-32.93180320174969</v>
+        <v>-31.83194554866274</v>
       </c>
       <c r="F95">
-        <v>-5.612545499197362</v>
+        <v>-5.501103575763939</v>
       </c>
       <c r="G95">
-        <v>-2.738951207674497</v>
+        <v>-0.7076931600527963</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-10.65310729055429</v>
       </c>
       <c r="E96">
-        <v>-35.01469746394771</v>
+        <v>-34.29352892127819</v>
       </c>
       <c r="F96">
-        <v>-5.812829826581032</v>
+        <v>-5.710494146006584</v>
       </c>
       <c r="G96">
-        <v>-3.638995844527233</v>
+        <v>-1.321302775756711</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-10.55564654541289</v>
       </c>
       <c r="E97">
-        <v>-37.35125872615939</v>
+        <v>-37.41394639184757</v>
       </c>
       <c r="F97">
-        <v>-6.104840933211497</v>
+        <v>-5.743643752731814</v>
       </c>
       <c r="G97">
-        <v>-3.446527347965085</v>
+        <v>-1.28024538997867</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-10.41842790606921</v>
       </c>
       <c r="E98">
-        <v>-39.98723816128423</v>
+        <v>-39.37651683542479</v>
       </c>
       <c r="F98">
-        <v>-5.908590755079461</v>
+        <v>-5.651007426076746</v>
       </c>
       <c r="G98">
-        <v>-3.530939638125422</v>
+        <v>-2.404940336580809</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-10.25096490154453</v>
       </c>
       <c r="E99">
-        <v>-43.27740548003113</v>
+        <v>-42.52253150532253</v>
       </c>
       <c r="F99">
-        <v>-6.452835594025361</v>
+        <v>-6.012439034531421</v>
       </c>
       <c r="G99">
-        <v>-3.770705898807138</v>
+        <v>-2.528473343378713</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-10.03455767671907</v>
       </c>
       <c r="E100">
-        <v>-45.26384777433979</v>
+        <v>-44.58440685541395</v>
       </c>
       <c r="F100">
-        <v>-5.88677404279193</v>
+        <v>-5.782828844353842</v>
       </c>
       <c r="G100">
-        <v>-4.375231377551292</v>
+        <v>-3.267221580467079</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-9.802563145630263</v>
       </c>
       <c r="E101">
-        <v>-47.77497944531016</v>
+        <v>-47.61494770235309</v>
       </c>
       <c r="F101">
-        <v>-6.226926549403491</v>
+        <v>-6.024082566745171</v>
       </c>
       <c r="G101">
-        <v>-5.358658724901652</v>
+        <v>-3.675835595288243</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-9.519868459309825</v>
       </c>
       <c r="E102">
-        <v>-50.08523366989278</v>
+        <v>-49.49532407845409</v>
       </c>
       <c r="F102">
-        <v>-5.822968215223895</v>
+        <v>-5.875753442865085</v>
       </c>
       <c r="G102">
-        <v>-6.08875981704144</v>
+        <v>-3.972791530160869</v>
       </c>
     </row>
   </sheetData>
